--- a/data/trans_bre/IP12-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP12-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 6,27</t>
+          <t>-6,57; 5,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 9,37</t>
+          <t>-4,26; 10,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 15,42</t>
+          <t>0,83; 15,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,46; 3,66</t>
+          <t>-15,3; 3,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-67,36; 220,94</t>
+          <t>-69,22; 173,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-42,93; 221,86</t>
+          <t>-40,41; 249,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-28,18; 1441,03</t>
+          <t>-26,18; 1204,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-83,95; 74,66</t>
+          <t>-85,46; 72,19</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 3,07</t>
+          <t>-2,29; 3,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 1,52</t>
+          <t>-4,4; 1,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 2,04</t>
+          <t>-3,15; 2,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 2,33</t>
+          <t>-3,57; 2,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,95; 58,58</t>
+          <t>-27,79; 58,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,83; 21,67</t>
+          <t>-41,25; 24,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,35; 35,04</t>
+          <t>-35,83; 37,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,85; 41,03</t>
+          <t>-40,33; 34,97</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 2,56</t>
+          <t>-5,25; 2,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 8,32</t>
+          <t>-1,86; 8,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 9,12</t>
+          <t>0,05; 8,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 5,53</t>
+          <t>-4,4; 5,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-63,04; 69,47</t>
+          <t>-62,46; 65,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-20,05; 184,0</t>
+          <t>-26,22; 186,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 239,78</t>
+          <t>-3,19; 285,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-47,3; 112,52</t>
+          <t>-42,88; 110,67</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 2,14</t>
+          <t>-2,35; 1,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 2,55</t>
+          <t>-2,34; 2,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 3,59</t>
+          <t>-0,92; 3,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 1,82</t>
+          <t>-3,49; 1,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,26; 41,53</t>
+          <t>-31,31; 34,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,88; 34,39</t>
+          <t>-23,84; 33,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 66,05</t>
+          <t>-13,28; 69,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,86; 29,71</t>
+          <t>-37,44; 24,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP12-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP12-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolores o síntomas</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolores o síntomas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 5,97</t>
+          <t>-6,08; 6,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 10,43</t>
+          <t>-5,5; 9,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 15,77</t>
+          <t>1,13; 16,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,3; 3,7</t>
+          <t>-13,76; 3,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-69,22; 173,52</t>
+          <t>-70,7; 188,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-40,41; 249,05</t>
+          <t>-48,37; 188,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-26,18; 1204,07</t>
+          <t>-8,38; 1317,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-85,46; 72,19</t>
+          <t>-81,91; 77,9</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 3,06</t>
+          <t>-2,4; 3,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 1,72</t>
+          <t>-4,36; 1,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 2,21</t>
+          <t>-3,36; 2,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 2,07</t>
+          <t>-3,77; 2,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,79; 58,86</t>
+          <t>-30,24; 56,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,25; 24,61</t>
+          <t>-41,32; 19,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,83; 37,86</t>
+          <t>-37,61; 38,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-40,33; 34,97</t>
+          <t>-40,72; 35,05</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 2,65</t>
+          <t>-5,42; 2,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 8,22</t>
+          <t>-2,07; 8,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 8,96</t>
+          <t>-0,07; 9,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 5,4</t>
+          <t>-4,63; 5,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-62,46; 65,1</t>
+          <t>-64,39; 61,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,22; 186,18</t>
+          <t>-25,98; 190,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 285,95</t>
+          <t>-4,25; 242,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-42,88; 110,67</t>
+          <t>-46,94; 116,67</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 1,97</t>
+          <t>-2,29; 1,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 2,49</t>
+          <t>-2,29; 2,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 3,61</t>
+          <t>-0,75; 3,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 1,59</t>
+          <t>-3,15; 1,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,31; 34,83</t>
+          <t>-30,09; 32,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,84; 33,44</t>
+          <t>-25,07; 37,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 69,14</t>
+          <t>-9,82; 68,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,44; 24,73</t>
+          <t>-34,71; 23,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP12-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP12-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-4,51</t>
+          <t>-4,58</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-40,91%</t>
+          <t>-39,24%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 6,2</t>
+          <t>-6,08; 6,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 9,38</t>
+          <t>-4,64; 9,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 16,47</t>
+          <t>0,9; 15,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 3,7</t>
+          <t>-14,11; 4,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-70,7; 188,64</t>
+          <t>-67,36; 220,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-48,37; 188,18</t>
+          <t>-42,93; 221,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 1317,21</t>
+          <t>-28,18; 1441,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-81,91; 77,9</t>
+          <t>-83,6; 89,44</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,53</t>
+          <t>-0,36</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-7,03%</t>
+          <t>-4,73%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 3,09</t>
+          <t>-2,36; 3,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 1,42</t>
+          <t>-4,61; 1,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 2,32</t>
+          <t>-3,21; 2,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 2,19</t>
+          <t>-3,58; 2,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,24; 56,44</t>
+          <t>-28,95; 58,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,32; 19,35</t>
+          <t>-41,83; 21,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,61; 38,73</t>
+          <t>-37,35; 35,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-40,72; 35,05</t>
+          <t>-38,38; 44,7</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 2,52</t>
+          <t>-5,52; 2,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 8,32</t>
+          <t>-1,42; 8,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 9,04</t>
+          <t>0,08; 9,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 5,47</t>
+          <t>-4,77; 5,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-64,39; 61,53</t>
+          <t>-63,04; 69,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-25,98; 190,9</t>
+          <t>-20,05; 184,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 242,05</t>
+          <t>-8,78; 239,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-46,94; 116,67</t>
+          <t>-46,18; 119,59</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,64</t>
+          <t>-0,48</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-8,21%</t>
+          <t>-6,09%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 1,9</t>
+          <t>-1,95; 2,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 2,58</t>
+          <t>-2,1; 2,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 3,63</t>
+          <t>-0,75; 3,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,59</t>
+          <t>-3,0; 2,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,09; 32,98</t>
+          <t>-26,26; 41,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,07; 37,35</t>
+          <t>-21,88; 34,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 68,11</t>
+          <t>-10,04; 66,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,71; 23,72</t>
+          <t>-32,5; 32,8</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP12-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP12-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,12</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,72</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7,82</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-4,58</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,83%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>33,2%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>239,65%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-39,24%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.1158840189885754</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.71507337060615</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>7.819357106893318</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-4.582067058441336</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.01828625907887233</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.3320430339475809</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>2.396531316072731</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.3924038634164699</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-6,08; 6,27</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-4,64; 9,37</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,9; 15,42</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-14,11; 4,37</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-67,36; 220,94</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-42,93; 221,86</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-28,18; 1441,03</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-83,6; 89,44</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-6.083685106173734</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-4.636324268239098</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.898907629868693</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-14.11018417569657</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.6735819590980792</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.4292858992795988</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.2817626958526588</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.8360181226976683</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>6.266678876693126</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>9.367590660606597</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>15.42274374888747</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>4.374542365150029</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>2.209355034592828</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>2.218607677498333</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>14.41025412478909</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.894356672148688</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,41</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,57</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,36</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-15,39%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-7,64%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-4,73%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,36; 3,07</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,61; 1,52</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,21; 2,04</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-3,58; 2,64</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-28,95; 58,58</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-41,83; 21,67</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-37,35; 35,04</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-38,38; 44,7</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.4047009226196344</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.410065190090416</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.5682548343056676</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.3607704941214374</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.06026192196287261</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.1539244931254441</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.07636171855422677</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.04727284357749994</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-1,29</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,19</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4,42</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,56</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-20,75%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>48,93%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>83,91%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>7,55%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.360467079876445</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-4.614441387157572</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.206327497782403</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-3.584732139265594</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.2894686148471983</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4182861045486151</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.3734688617035717</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.383808869722185</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-5,52; 2,56</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-1,42; 8,32</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,08; 9,12</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-4,77; 5,89</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-63,04; 69,47</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-20,05; 184,0</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-8,78; 239,78</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-46,18; 119,59</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.065577565375919</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.523144646661359</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.036925801879709</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.641315146721812</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.5858241893918852</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.2166856609947999</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.3504036699155418</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.446982231935167</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +819,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,12</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,41</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,48</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-1,85%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>21,65%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-6,09%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-1.293141339172998</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3.187150773352939</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>4.41871606462281</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.5594200847173256</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.2074919765660253</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.4893312407117863</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.8391083884040672</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.07551061737272406</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,95; 2,14</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,1; 2,55</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-0,75; 3,59</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-3,0; 2,05</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-26,26; 41,53</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-21,88; 34,39</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-10,04; 66,05</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-32,5; 32,8</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-5.523796592803683</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-1.419841777357116</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.07598655665674724</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-4.772730358350106</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.6304251438239474</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.2005018925075554</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.08780390822683086</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.4618281279753421</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2.560611260893506</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>8.322061863320233</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>9.124751999341449</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>5.892161645825488</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.6947358636593087</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.839974727495407</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>2.397809200973528</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.19586165317495</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.1213698862284618</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1732777205815036</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.40937149207503</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.4813343103676204</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.01848944652922895</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.02052452479866216</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.2165263762158409</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.0608860130098333</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.954320204597513</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.096972305664562</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.7479569944202287</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-3.004879924683153</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2626113353982806</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.218837159483181</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1003701485290753</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.3249989174236192</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.138692162403305</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.548813335992924</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.592376150912641</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.054123801022387</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.4153422330558426</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.343852279912657</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.6605083465516295</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.3280340030130464</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1017,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
